--- a/app/templates/informes/Humedad ASTM D2216-19/Template_ContHumedad_D2216.xlsx
+++ b/app/templates/informes/Humedad ASTM D2216-19/Template_ContHumedad_D2216.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\crmnew\api-geofal-crm\app\templates\informes\ContHumedad\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\3.0 Formatos e informes\2026\1.0 Informe de ensayo\1.1 Informe Suelo\INFORME ACREDITADO-E ISO\6.1 JUNIO INICIA 15-06-25\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{422D366B-0E4F-48EF-A099-1BA65A2E2032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DDB3D68-FEBC-4342-B44F-783BD39595B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="723" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1259,7 +1259,7 @@
     <numFmt numFmtId="186" formatCode="000\-\ &quot;26&quot;"/>
     <numFmt numFmtId="187" formatCode="&quot;FORMATO F-LEM-P-SU-11.01&quot;"/>
   </numFmts>
-  <fonts count="83">
+  <fonts count="82">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1772,12 +1772,6 @@
       <u/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -2472,7 +2466,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="708">
+  <cellXfs count="707">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4787,10 +4781,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="10">
@@ -5036,7 +5026,7 @@
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="77591296"/>
@@ -5072,7 +5062,7 @@
                 <a:cs typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
+            <a:endParaRPr lang="es-ES"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="77557120"/>
@@ -5110,7 +5100,7 @@
           <a:cs typeface="Calibri"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
+      <a:endParaRPr lang="es-ES"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -6533,7 +6523,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -6592,7 +6582,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="datos de ecuacion del anillo"/>
@@ -6711,7 +6701,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -6762,7 +6752,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -6814,7 +6804,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="BGA"/>
@@ -6846,7 +6836,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="-------"/>
@@ -11730,7 +11720,6 @@
       <c r="N53" s="317"/>
     </row>
     <row r="54" spans="1:17">
-      <c r="H54" s="707"/>
       <c r="M54" s="186"/>
       <c r="N54" s="317"/>
     </row>
@@ -12034,6 +12023,7 @@
       <c r="N94" s="317"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="zMsqYySmwKFoFPvTnU0pM2iBYqllvXmKPWKxwHoZdI/aNMm5lQzC8Oi9/JSS/KLlzDghQdKjvcwPX1SyVjT0Tw==" saltValue="Ot/YrcHkrPx+Qo/6ciN67w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
     <protectedRange sqref="E7:F9 E12:F12" name="Rango3_3_1_1_1_1_1_1_1_1"/>
     <protectedRange sqref="E5:F6" name="Rango3_3_1_1_1_1_1_2_1"/>
